--- a/www/download/IND.compensation.empe.s.us.rpA1.xlsx
+++ b/www/download/IND.compensation.empe.s.us.rpA1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>189868.494299314</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>213941.082808452</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>211949.947596942</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>190483.508639969</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>205915.128769095</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>197591.943818719</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>184329.016168008</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>204239.350027981</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>260832.844519709</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>317552.901824903</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>354812.091731048</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>383147.040357706</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>462040.19248977</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>511098.123781348</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>498689.56142909</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>127992.186669422</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123152.953138419</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108742.303558698</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>111117.858937595</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>110147.54241072</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98683.3827996589</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97497.3858792404</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>104707.904963036</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>127950.733972506</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>143456.680272801</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>148695.16079702</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>157113.790745812</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>180261.99366911</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>204525.199765735</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>194288.149892041</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>145787.436978897</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>141086.82183962</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>127201.43659137</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129745.94339465</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>130798.806343329</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118625.892780869</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121459.216405026</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>133173.760639047</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>162243.029399309</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>183289.402962845</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>189538.754053939</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>200242.206394935</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>229984.011665091</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>260066.435398422</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>249276.082989467</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5489.46630861788</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5006.89951687757</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3785.66597417408</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4945.03266376072</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4798.34269918028</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4380.49479616497</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4758.44007447194</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5335.1763633511</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6958.43965857143</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8259.53538536535</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9075.80306826029</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10152.1320669268</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13383.0860932627</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17345.3482740352</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17471.3095980248</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>328022.217561222</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>357050.860492582</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>359800.07234588</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>354405.445036471</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>243070.117973706</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>261244.890042264</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226361.85432922</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>208054.975411469</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>219695.42882029</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>261347.622060217</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>355201.572591124</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>445629.031897406</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>564910.169945729</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>691295.03710285</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>706701.547310895</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>305138.4016117</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>314440.841405294</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>327587.594007179</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>321065.947049094</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>338738.67643198</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>367677.601538057</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>368676.021467726</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>378844.950791367</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>445424.810033035</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>506864.549157474</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>575007.827669293</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>655840.40661744</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>729298.239529298</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>780052.462522621</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>691872.689819192</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>397856.131927165</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>467727.886435222</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>515800.335953662</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>542539.536153294</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>563860.76736749</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>607903.674040208</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>659006.88251917</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>707407.939686337</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>777143.095397519</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>900055.312694353</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>1018459.84835292</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.182</t>
+          <t>1182195.15416825</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1468707.44826045</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.906</t>
+          <t>1905657.48987876</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.088</t>
+          <t>2087894.22134836</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4009.30204461226</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4110.62893189141</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3985.18004554325</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4160.21885548685</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4226.76494684178</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3977.86902232336</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4095.1821265542</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4664.52482765077</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6094.95444184257</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7135.12399070072</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7639.76272830467</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8245.92046224411</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9545.39955151358</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11024.2451353322</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10604.365021569</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18220.6268033519</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27187.0100592577</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25267.2653929607</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26126.5752365978</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25163.5732089882</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23884.7725715342</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26170.0574150603</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32666.5579290532</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40090.0440019927</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46874.1269933221</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53686.4442984798</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>61450.9121663255</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74981.2805796816</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>95746.3264610447</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83007.720834956</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>1363254.26397007</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1310121.86457592</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.143</t>
+          <t>1142969.47780482</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1150434.99498854</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>1130675.20037073</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.017</t>
+          <t>1017493.19579972</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.005</t>
+          <t>1005060.25879547</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.068</t>
+          <t>1068159.18640789</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.282</t>
+          <t>1281841.85530205</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1415296.91437412</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>1406878.01531334</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.444</t>
+          <t>1443676.29595017</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1617724.45786562</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.809</t>
+          <t>1809250.3412473</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.735</t>
+          <t>1734712.46695596</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94971.4486076223</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96628.980039683</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89063.7497972945</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92950.5213038583</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93612.2728596442</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>84412.844093664</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86209.8718097497</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>94381.1111311811</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>115950.35382168</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>131238.165489814</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137583.502637156</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>146652.503161933</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>170947.778596475</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>192843.389463581</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>184367.104605978</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>291808.316733849</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>305132.106559137</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>284654.105695089</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>297978.063926283</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>306337.553877687</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>288325.761286174</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>299763.592259955</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>335934.791999997</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>428228.190224466</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>498930.754307214</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>535998.080271348</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>583286.457455248</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>688240.415189618</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>783200.673539864</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>727079.091269295</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1978.1820783021</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2362.18888529114</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2442.55657145964</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2664.76063660272</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2648.09972342715</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2575.89638618198</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2771.60707940775</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3248.67343257762</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4366.19409573783</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5336.24859621905</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6151.02077167553</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7459.21239006176</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10097.8506948805</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12308.5231619955</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10312.433995032</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64780.1545720892</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64117.2790306618</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59836.0697050603</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62504.8914512194</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62601.8923411265</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57618.7875727284</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59520.6814993623</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64725.3726908649</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79674.9373851652</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91179.109613634</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>95969.8720259783</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101251.582030597</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>117111.963314036</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>133967.8212127</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>126339.07733036</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>814431.400719446</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>816271.905844365</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>734763.548543567</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>754329.977991125</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>755497.618081448</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>690557.264864149</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>699934.70624591</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>769508.450167643</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.947</t>
+          <t>947369.787305278</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>1078060.71345106</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>1117592.42423547</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.176</t>
+          <t>1176401.75190837</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1335242.48594087</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.486</t>
+          <t>1485590.23912755</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.408</t>
+          <t>1407887.81680612</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>609344.664262209</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>630766.500194064</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>704156.9451464</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>772019.549801978</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>802302.130258525</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>806841.874751881</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>812416.796848852</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>881834.139782243</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.008</t>
+          <t>1008231.40487965</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>1188319.79474407</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.246</t>
+          <t>1246278.60661961</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.327</t>
+          <t>1327141.80120477</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1520317.19677425</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1439534.76037267</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.223</t>
+          <t>1222888.6709742</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42013.1707374524</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43965.1707252105</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44094.2960000242</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44965.6765175738</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47241.814729578</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42409.5159224413</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42875.220364943</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52357.9240787107</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67858.6070569255</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80668.4721738653</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>85337.7830020339</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92697.5696416739</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>110178.122073115</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>127430.075197121</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>125213.580103711</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21148.7209385179</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20803.7284565732</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20896.892847196</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21375.3848137194</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21042.4432893277</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20903.7686172109</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23865.8383132277</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30331.645055342</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38730.082244585</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46963.7342737843</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51508.7043663024</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52097.0567684416</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63835.9978007698</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71859.7339886758</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58694.778280572</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74685.9170336728</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>85768.7808002433</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>85466.0101454388</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32372.7188251886</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49043.8056157691</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52170.1354876091</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51127.5688411985</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62032.9060123352</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74664.3211104431</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78881.0507419105</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86065.0585550075</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>114791.24778633</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>135475.775248298</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>159754.246728171</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>170476.095240995</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>123613.527569007</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>120048.866053424</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139339.845934098</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>139753.09091733</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>146077.221231</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>148492.076719936</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>152614.816485931</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>157697.743396309</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>182469.015584059</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>210392.821080105</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>245138.93048999</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>272797.882795781</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>337414.481954298</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>368490.321395703</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>386510.154509205</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30216.7274515467</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32858.690471087</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34730.506188777</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36928.6783913506</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39231.0631348185</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38677.4118061508</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41788.0281601937</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47294.7074669603</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>61157.1850026985</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73200.7446860464</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>82179.909290841</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91298.543601515</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>107930.941673357</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>123709.969852541</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>106941.324329402</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>465340.671482329</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>521488.798651422</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>496303.293015968</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>483449.282630376</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>477855.563537439</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>431683.994937708</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>441795.012050519</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>487938.915002717</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>606583.421349111</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>690968.940876866</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>724059.701269968</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>764489.446355203</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>867055.557783028</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.968</t>
+          <t>967793.77757274</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>912973.106233138</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2.745</t>
+          <t>2745397.56350226</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.356</t>
+          <t>2356418.57498836</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2.155</t>
+          <t>2155235.27917576</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.968</t>
+          <t>1967747.36004907</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.207</t>
+          <t>2207154.36040258</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2.356</t>
+          <t>2355518.11130577</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2070012.8644661</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.957</t>
+          <t>1956912.12619623</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2.093</t>
+          <t>2092714.68105092</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.273</t>
+          <t>2272852.69144693</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2250071.87505063</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.181</t>
+          <t>2181417.80457924</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2.184</t>
+          <t>2184132.6284078</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.427</t>
+          <t>2427079.55996368</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.468</t>
+          <t>2467893.18097585</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>249110.987205519</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>272393.548705949</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>249618.697610976</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>161334.261309919</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>200645.101910896</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>229288.854944361</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>219964.217061377</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>250739.517668645</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>287975.197009048</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>322535.656092378</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>387647.803112496</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>440293.28298971</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>483677.734658298</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>439426.781156843</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>390590.697894541</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2504.97500744375</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3185.72497070167</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3915.82503481901</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4674.57499957807</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4707.72500997286</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4508.299991816</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4631.35001721752</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5473.03260370754</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7280.6121051987</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9086.21960703123</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10621.4053437327</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12904.6207284722</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16887.3322519144</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21323.5323202352</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16682.5566681587</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9740.1412712637</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9686.90523316738</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8888.96000180688</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9260.24573072016</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9707.83884539053</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9383.86853228874</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9974.92436313154</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11218.0306068978</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13832.6523549874</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16090.9651895715</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17349.0987159548</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18656.0812384003</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22113.8396061466</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27381.5534351554</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26920.620660565</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2172.24091164139</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2606.77053933799</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2747.62816097584</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2945.32700799828</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3174.87626423622</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3233.40231233089</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3291.34126466962</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3580.18221014853</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4422.86729020185</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5410.66785573386</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6706.90624696575</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8739.59498049103</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13482.0947985381</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17141.6124501607</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12000.9795323206</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97455.7494096245</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>104490.046105522</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129780.475950205</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>141385.448509669</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>163673.430974625</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>198534.708527231</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>220366.953413951</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>229946.714188716</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>219849.811630637</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>225131.026493785</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>250505.955256056</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>271224.470360002</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>290200.212538196</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>306949.737800774</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>249769.412214035</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1616.02247943738</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1715.50960720146</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1667.34448396809</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1754.22786698853</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1785.88735535493</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1708.42222994882</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1795.89572328168</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1963.83622744647</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2341.0084328578</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2657.18545419359</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2726.00838892361</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2910.50556607688</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3330.69237946551</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4211.27127438239</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3969.63156938789</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>214079.514468347</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>211595.833904053</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>193626.391223694</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>204747.186797824</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>210329.226889465</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>195621.254394251</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>203650.489479185</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>225832.914828991</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>277994.651057547</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>312256.202294237</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>316701.821837909</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>332639.823540857</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>384163.475688043</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>434081.231334496</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>417675.806562603</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55322.2305835788</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64243.2401122611</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65817.015680837</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72614.0086731007</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>69775.9544477548</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69008.2517646412</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78158.5883185697</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77618.7934548832</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82843.1121536122</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91917.3966184302</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108968.128312447</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121452.55447037</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>151637.307249389</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>199382.989951675</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>158759.834349227</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54517.4651070032</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57330.1530302811</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55091.0606983683</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58355.0120387198</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59941.9741107586</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56378.2077130772</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57660.4321514658</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63999.5308730138</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78562.5165176056</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89326.0714626469</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93752.8850865868</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>100487.676195267</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113975.170066242</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>126619.355989369</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>119754.25756002</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14284.517009183</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14117.410760155</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11690.0745960578</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16021.0430218163</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12696.4634033637</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14925.8000167552</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16857.3288552141</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18209.382789563</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22301.843613053</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28061.4360667414</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38830.2546278648</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47134.0930612798</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66514.4530613812</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86485.0219131855</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66985.0361892292</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151159.009193339</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>185338.83086088</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>184975.256528038</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>140689.903431833</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81231.3104575208</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>105661.233291054</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>125423.120332758</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>147728.913971488</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>179894.454761889</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>240273.375587034</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>302330.993567352</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>392153.108558408</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>525840.489767422</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>674098.379990093</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>510927.635817245</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5894.25037387876</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6603.75080997851</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7040.07879467815</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7300.48399943145</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6386.01976775629</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6408.69031067664</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6434.05720682011</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7438.84156967545</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9969.87089404469</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12063.8341282007</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13882.2527629599</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16059.1275751979</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21385.5337672559</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27426.80672863</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26902.3427813828</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11620.1369238212</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11384.3056424847</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10709.4891936987</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11083.3810905755</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11180.7760355203</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10295.4488956846</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10625.4286805587</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11845.1108065973</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14830.0951715441</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17269.3779092422</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18247.4300526506</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19678.4004124698</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23588.5602801829</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27890.5342784981</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26281.4710697563</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>133127.784362746</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>150511.0878089</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136807.643597456</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>137032.009325101</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>136351.930258648</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>135897.23871761</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>128638.440508168</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>140953.50530439</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>174679.259001201</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>198006.744264434</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>201662.713361205</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>211588.521117675</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>248571.027188134</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>262905.781776772</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>222136.709758279</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46762.503304833</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55367.2707665812</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63001.6664133908</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64297.3387244751</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73322.4637282348</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73219.3651377562</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53765.6546316908</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53901.3390008949</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>69526.7132388374</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89150.8864842486</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>111455.986843736</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121229.481071189</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149940.04512114</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171134.668985618</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>142983.455042068</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139276.624928551</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>146385.999045722</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149823.721510242</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134565.297386867</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>143785.405090095</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>154526.466639178</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>141412.000266344</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137943.195527433</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>142429.711039491</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>152115.099336601</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>165805.900278924</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>172048.156420619</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>175788.537823953</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>183824.014436678</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>169371.52751886</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.111</t>
+          <t>4111271.34380874</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4.319</t>
+          <t>4319358.82722058</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4589681.86829822</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>4.908</t>
+          <t>4907901.94376541</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5.214</t>
+          <t>5214254.20605125</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5.636</t>
+          <t>5636194.04466866</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5.846</t>
+          <t>5845754.13298404</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>5.991</t>
+          <t>5990808.40708692</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6259694.94570284</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>6.575</t>
+          <t>6574879.48097678</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>6.954</t>
+          <t>6954263.47887655</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>7.354</t>
+          <t>7354289.12302536</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>7.764</t>
+          <t>7764091.97723864</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>7980292.02050788</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>7.756</t>
+          <t>7755767.15769361</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.656</t>
+          <t>1656099.77634291</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.752</t>
+          <t>1752367.9646248</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.776</t>
+          <t>1775560.24831936</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.711</t>
+          <t>1710628.53985104</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>1729179.1735902</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.808</t>
+          <t>1808311.6142287</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.805</t>
+          <t>1805400.01718355</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1.777</t>
+          <t>1776618.243776</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1970113.47623266</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2.269</t>
+          <t>2268914.53320351</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2.609</t>
+          <t>2608844.29810359</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2.975</t>
+          <t>2975171.26753475</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>3.462</t>
+          <t>3462290.42564073</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4230212.3731713</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3950317.57228416</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>15.221</t>
+          <t>15221384.2665545</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>15.429</t>
+          <t>15429141.5996516</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>15.319</t>
+          <t>15318515.8241342</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>15.331</t>
+          <t>15330655.2517422</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15900170.5237955</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>16.435</t>
+          <t>16434756.3332771</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>16.416</t>
+          <t>16415915.2920473</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>16.947</t>
+          <t>16947272.3259557</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18.855</t>
+          <t>18854816.2148648</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>20.892</t>
+          <t>20892271.5702224</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>22.393</t>
+          <t>22393234.0699656</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>24.078</t>
+          <t>24078135.639353</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>26.916</t>
+          <t>26916296.3842254</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29800411.7686462</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28449891.2350189</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>compensation.empe.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
